--- a/planilhas/Painel-Turma-LUDUS.xlsx
+++ b/planilhas/Painel-Turma-LUDUS.xlsx
@@ -682,7 +682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -770,7 +770,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>NOTA %</t>
+          <t>QUIZ %</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -905,7 +905,7 @@
         <v/>
       </c>
       <c r="T4" s="8">
-        <f>IF($J4="","—",IF($J4&gt;=75,"ok — avança e volta ao A",IF($I4&gt;=2,"⚠ esgotou as 2 tentativas — você libera","abaixo de 75 — cabe 2ª tentativa")))</f>
+        <f>IF($J4="","—",IF($J4&gt;=75,"ok — avança e volta ao A",IF($I4&gt;=2,"⚠ 2 tentativas sem passar — converse antes da próxima","abaixo de 75 — pode refazer")))</f>
         <v/>
       </c>
       <c r="U4" s="9">
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="T5" s="8">
-        <f>IF($J5="","—",IF($J5&gt;=75,"ok — avança e volta ao A",IF($I5&gt;=2,"⚠ esgotou as 2 tentativas — você libera","abaixo de 75 — cabe 2ª tentativa")))</f>
+        <f>IF($J5="","—",IF($J5&gt;=75,"ok — avança e volta ao A",IF($I5&gt;=2,"⚠ 2 tentativas sem passar — converse antes da próxima","abaixo de 75 — pode refazer")))</f>
         <v/>
       </c>
       <c r="U5" s="9">
@@ -1073,7 +1073,7 @@
         <v/>
       </c>
       <c r="T6" s="8">
-        <f>IF($J6="","—",IF($J6&gt;=75,"ok — avança e volta ao A",IF($I6&gt;=2,"⚠ esgotou as 2 tentativas — você libera","abaixo de 75 — cabe 2ª tentativa")))</f>
+        <f>IF($J6="","—",IF($J6&gt;=75,"ok — avança e volta ao A",IF($I6&gt;=2,"⚠ 2 tentativas sem passar — converse antes da próxima","abaixo de 75 — pode refazer")))</f>
         <v/>
       </c>
       <c r="U6" s="9">
@@ -1157,7 +1157,7 @@
         <v/>
       </c>
       <c r="T7" s="8">
-        <f>IF($J7="","—",IF($J7&gt;=75,"ok — avança e volta ao A",IF($I7&gt;=2,"⚠ esgotou as 2 tentativas — você libera","abaixo de 75 — cabe 2ª tentativa")))</f>
+        <f>IF($J7="","—",IF($J7&gt;=75,"ok — avança e volta ao A",IF($I7&gt;=2,"⚠ 2 tentativas sem passar — converse antes da próxima","abaixo de 75 — pode refazer")))</f>
         <v/>
       </c>
       <c r="U7" s="9">
@@ -1182,7 +1182,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Depois da sessão, no debrief: marque sim/não em LIÇÃO DE CASA, USOU O FOCUS e APRESENTOU. A coluna LP é o que o aluno terá para gastar NA PRÓXIMA sessão.</t>
+          <t>Depois da sessão, no debrief: marque sim/não em LIÇÃO DE CASA, USOU O FOCUS e APRESENTOU. A coluna LP é o que o aluno terá para gastar NA PRÓXIMA sessão — anuncie em voz alta, e é o aluno que anota na ficha dele.</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Uma vez por semana, lance TENTATIVAS e NOTA lendo o relatório do Cambridge One.</t>
+          <t>Uma vez por semana, lance TENTATIVAS e NOTA lendo as respostas do Unit Quiz no Google Forms. A lição de casa fica no Cambridge One e a plataforma corrige sozinha — você não lança nada dela.</t>
         </is>
       </c>
     </row>
@@ -1206,22 +1206,15 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GRUPOS DE UM ENCONTRO POR SEMANA cobrem DUAS lições do ciclo por encontro: avance a coluna LIÇÃO duas vezes.</t>
+          <t>UMA HORA DE AULA = UMA LIÇÃO DO CICLO. Grupo de um encontro de 2h avança a coluna LIÇÃO duas vezes; grupo de dois encontros de 1h avança uma vez por encontro. Todo grupo faz duas lições por semana e uma unidade a cada duas semanas — não existe formato mais rápido.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>GRUPOS DE DOIS ENCONTROS cobrem UMA lição por encontro: avance uma vez. O ciclo conta lições, não dias.</t>
-        </is>
-      </c>
+      <c r="A16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>NADA das colunas I, J e T sai deste arquivo. O Quadro da Turma só enxerga a aba QUADRO.</t>
         </is>
@@ -1238,7 +1231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1290,7 +1283,7 @@
       </c>
       <c r="H1" s="5" t="inlineStr">
         <is>
-          <t>LANG. POINTS</t>
+          <t>LP PARA ESTA SESSÃO</t>
         </is>
       </c>
       <c r="I1" s="5" t="inlineStr">
@@ -1476,6 +1469,13 @@
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Não digite nada aqui: as nove colunas são espelho do PAINEL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>A coluna LP é o que você anunciou no debrief passado. Quem controla o saldo durante a sessão é o aluno, na ficha dele — esta coluna é a conferência, não o placar.</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>is/are (afirm. e pergunta)</t>
+          <t>is/are (affirmative and question forms)</t>
         </is>
       </c>
       <c r="G3" s="12" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="J3" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>possessive 's e s'; It is</t>
+          <t>possessive 's and s'; It is</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>pergunta sim/não</t>
+          <t>yes/no questions</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Present continuous (afirm. e pergunta)</t>
+          <t>Present continuous (affirmative and question forms)</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>⚠ conferir no livro — o catálogo traz um tópico só</t>
+          <t>⚠ check the book — the catalogue gives only one topic</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>can/can't (habilidade e possibilidade)</t>
+          <t>can/can't (ability and possibility)</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>be going to (afirm. e pergunta)</t>
+          <t>be going to (affirmative and question forms)</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>⚠ conferir no livro — o catálogo traz um tópico só</t>
+          <t>⚠ check the book — the catalogue gives only one topic</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>was/were (afirm. e pergunta)</t>
+          <t>was/were (affirmative and question forms)</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>⚠ conferir no livro — o catálogo traz um tópico só</t>
+          <t>⚠ check the book — the catalogue gives only one topic</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Simple past (afirm. e pergunta)</t>
+          <t>Simple past (affirmative and question forms)</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>possessive adjectives e pronouns; possessive 's</t>
+          <t>possessive adjectives and pronouns; possessive 's</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>Simple present (hábitos)</t>
+          <t>Simple present (habits)</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>contraste simple present x continuous</t>
+          <t>simple present vs continuous</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Present continuous (planos futuros)</t>
+          <t>Present continuous (future plans)</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2349,12 +2349,12 @@
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Simple past (afirm., neg. e pergunta)</t>
+          <t>Simple past (affirmative, negative and question forms)</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>⚠ conferir no livro — o catálogo traz um tópico só</t>
+          <t>⚠ check the book — the catalogue gives only one topic</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>⚠ conferir no livro — o catálogo traz um tópico só</t>
+          <t>⚠ check the book — the catalogue gives only one topic</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>predictions com will/may/might</t>
+          <t>predictions with will/may/might</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Present perfect (experiências)</t>
+          <t>Present perfect (experiences)</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>will (decisão súbita); present continuous (futuro)</t>
+          <t>will (sudden decisions); present continuous (future)</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>real conditionals (presente e futuro)</t>
+          <t>real conditionals (present and future)</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>contraste com present perfect</t>
+          <t>contrast with present perfect</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>Modais de necessidade</t>
+          <t>Modals of necessity</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>modais de proibição e permissão</t>
+          <t>modals of prohibition and permission</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>unreal conditionals (presente e futuro)</t>
+          <t>unreal conditionals (present and future)</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>Tense review (simple e continuous)</t>
+          <t>Tense review (simple and continuous)</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>clauses com after/until/when</t>
+          <t>clauses with after/until/when</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>passive com modals</t>
+          <t>passive with modals</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>Prohibition, permission e obligation (presente e passado)</t>
+          <t>Prohibition, permission and obligation (present and past)</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>⚠ conferir no livro — o catálogo traz um tópico só</t>
+          <t>⚠ check the book — the catalogue gives only one topic</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>Gerund/infinitive após forget/remember/stop</t>
+          <t>Gerund/infinitive after forget/remember/stop</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>Comparative e superlative structures</t>
+          <t>Comparative and superlative structures</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>reported speech com modal verbs</t>
+          <t>reported speech with modal verbs</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4173,12 +4173,12 @@
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>Gerunds e infinitives após adjectives, nouns e pronouns</t>
+          <t>Gerunds and infinitives after adjectives, nouns and pronouns</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>⚠ conferir no livro — o catálogo traz um tópico só</t>
+          <t>⚠ check the book — the catalogue gives only one topic</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>Modal-like expressions com "by"</t>
+          <t>Modal-like expressions with "by"</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>Gerunds após preposições</t>
+          <t>Gerunds after preposições</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>Passives com modais e modal-like expressions</t>
+          <t>Passives with modals and modal-like expressions</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>Adverbs com adjectives e adverbs</t>
+          <t>Adverbs with adjectives and adverbs</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>future perfect e future continuous</t>
+          <t>future perfect and future continuous</t>
         </is>
       </c>
       <c r="H62" s="12" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="J62" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="J63" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>Variações de past unreal conditionals</t>
+          <t>Variations on past unreal conditionals</t>
         </is>
       </c>
       <c r="G64" s="12" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>Quantifiers e prepositions em relative clauses</t>
+          <t>Quantifiers and prepositions in relative clauses</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="J65" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>question words com "-ever"</t>
+          <t>question words with "-ever"</t>
         </is>
       </c>
       <c r="H67" s="12" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="J67" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>Negative e limiting adverbials</t>
+          <t>Negative and limiting adverbials</t>
         </is>
       </c>
       <c r="G68" s="12" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="J68" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4797,12 +4797,12 @@
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>Phrases com "get"</t>
+          <t>Phrases with "get"</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>phrases com "go"</t>
+          <t>phrases with "go"</t>
         </is>
       </c>
       <c r="H69" s="12" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="J69" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="J70" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="J71" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="J72" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="J73" s="12" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>conferida</t>
         </is>
       </c>
     </row>
